--- a/daily_matches/job_matches_2026-08-27.xlsx
+++ b/daily_matches/job_matches_2026-08-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Platform Engineer-Anthropic-US East</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NewRocket</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Woodbridge, VA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>27.8</v>
+        <v>23.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Pinecone, MLflow, Docker, Kubernetes, CI/CD</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,67 +496,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e38dcb9b17b16495</t>
+          <t>https://www.indeed.com/viewjob?jk=2bf9322c6196fb9c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Platform Engineer-Anthropic-US West</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NewRocket</t>
+          <t>Ignite Insurance Systems</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Vista, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>27.8</v>
+        <v>22.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Pinecone, MLflow, Docker, Kubernetes, CI/CD</t>
+          <t>Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, XGBoost, AWS SageMaker, S3, EC2, Glue</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=669da4f7162d9233</t>
+          <t>https://www.indeed.com/viewjob?jk=cecaeb7f30f5319a</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Platform Engineer-Anthropic-US East</t>
+          <t>Senior Data Scientist - US</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NewRocket</t>
+          <t>mSupply</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>27.8</v>
+        <v>20</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Pinecone, MLflow, Docker, Kubernetes, CI/CD</t>
+          <t>Data Scientist, RAG, XGBoost, LightGBM, Synapse, MLflow, Docker, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fec3742f5627ce31</t>
+          <t>https://www.indeed.com/viewjob?jk=31dc53c6e7bd5b4e</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>EQUS</t>
+          <t>J2B GLOBAL LLC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>18.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Mistral, Prompt Engineering, S3, MLflow, Docker, Kubernetes</t>
+          <t>Generative AI, LangChain, FastAPI, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6cecd3ad3a9d3e4</t>
+          <t>https://www.indeed.com/viewjob?jk=2e40611058ee4416</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Vision Engineer</t>
+          <t>Senior Data Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NEXXA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>18.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, Hugging Face, PyTorch, OpenCV, YOLO, Docker, Kubernetes, PostgreSQL, Python</t>
+          <t>Data Scientist, RAG, S3, Glue, Athena, Redshift, Kinesis, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b08f3107043b44a</t>
+          <t>https://www.indeed.com/viewjob?jk=bb602e905cf8e618</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Vision Engineer</t>
+          <t>Machine Learning Engineer II</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NEXXA</t>
+          <t>7-Eleven</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, Hugging Face, PyTorch, OpenCV, YOLO, Docker, Kubernetes, PostgreSQL, Python</t>
+          <t>Data Scientist, Machine Learning Engineer, XGBoost, Kubernetes, AKS, CI/CD, Git, Databricks, PySpark, Tableau</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b84b68284697e5c2</t>
+          <t>https://www.indeed.com/viewjob?jk=e74e8ed1040b80da</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cloud Transformation Senior Consultant</t>
+          <t>Senior AI/Machine Learning Engineer - Python | TheLoops</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>IFS</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,42 +696,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+          <t>AI Engineer, Machine Learning Engineer, LangChain, RAG, Copilot, Hugging Face, Pinecone, Prompt Engineering, CI/CD, Git</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d23da9f70702c22b</t>
+          <t>https://www.indeed.com/viewjob?jk=17ff5f1fcf1da2c4</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Backend AI Engineer</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NEXXA</t>
+          <t>WellRithms</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, OpenCV, Docker, Kubernetes, CI/CD, Kafka</t>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, FastAPI, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=009c3e95ad176788</t>
+          <t>https://www.indeed.com/viewjob?jk=e5067287c910f6c1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Backend AI Engineer</t>
+          <t>Software Engineer, Global Banking &amp; Markets, Trading Technology</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NEXXA</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, OpenCV, Docker, Kubernetes, CI/CD, Kafka</t>
+          <t>RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22605e962cd1fff7</t>
+          <t>https://www.indeed.com/viewjob?jk=3cf2f6c6ef1595cb</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Docker, CI/CD, Jenkins, GitHub Actions, Git, MongoDB, NoSQL, Python, SQL, R</t>
+          <t>Generative AI, RAG, Copilot, S3, Glue, Redshift, CI/CD, Git, Snowflake, Redshift</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,102 +811,102 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f79db46ebbc9c81b</t>
+          <t>https://www.indeed.com/viewjob?jk=c00d4d4ff843dddd</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Scientist - LLM Customization Team</t>
+          <t>Sr Engineer, FW &amp; Product Test</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Longmont, CO, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, Hugging Face, PyTorch, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=520ca44c564a0985</t>
+          <t>https://www.indeed.com/viewjob?jk=9dcae17fa0b18673</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI ENGINEER</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Davie, FL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Kinesis, Docker, CI/CD, GitHub Actions, Git, Kafka, MySQL, MongoDB, NoSQL</t>
+          <t>AI Engineer, Generative AI, RAG, TensorFlow, OpenCV, Git, Kafka, Hadoop, Tableau, Python</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a839e540347ca966</t>
+          <t>https://www.indeed.com/viewjob?jk=877bfa4f1917b570</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Engineer I- Software</t>
+          <t>Data Science (AI &amp; Machine Learning Intern)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>Sikka Software</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, S3, MLflow, CI/CD, Databricks, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Python</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,229 +916,229 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=868097f3e1f3cce9</t>
+          <t>https://www.indeed.com/viewjob?jk=042b97f18b78c43f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>DATA SCIENTIST</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bitsight</t>
+          <t>Sally Beauty</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, SQL</t>
+          <t>Data Scientist, RAG, MLflow, CI/CD, Git, Databricks, PySpark, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c83d416b1e6d8a65</t>
+          <t>https://www.indeed.com/viewjob?jk=42d679ea3c698d23</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Software Solutions Engineer - Measurement Instrumentation</t>
+          <t>DATA SCIENTIST</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Keysight Technologies</t>
+          <t>Sally Beauty</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, Git, Python, R, Java, Optimization</t>
+          <t>Data Scientist, RAG, MLflow, CI/CD, Git, Databricks, PySpark, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1da1dd7a8c28a0f</t>
+          <t>https://www.indeed.com/viewjob?jk=8796c5884589fa5a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>AI Developer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>HFB Technologies</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Torrance, CA, US USA</t>
+          <t>Saint George, UT, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, S3, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Java</t>
+          <t>LangChain, RAG, Gemini, Prompt Engineering, Docker, Kubernetes, Git, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf33c5c43beaa8e6</t>
+          <t>https://www.indeed.com/viewjob?jk=9ee067312582cb98</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Developer Relations</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ARANGO</t>
+          <t>VIABILITY, INC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Springfield, MA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Copilot, Docker, Kubernetes, Python, R, Java</t>
+          <t>LangChain, RAG, FastAPI, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0ac2dcf08fe30f9</t>
+          <t>https://www.indeed.com/viewjob?jk=51199e69247d222b</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data Integration Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GE HealthCare</t>
+          <t>Northwood Investors</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, TensorFlow, PyTorch, Git, Hadoop, Python, R, Java, Scala</t>
+          <t>RAG, Cortex, S3, CI/CD, Snowflake, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45c91f4f46f8f794</t>
+          <t>https://www.indeed.com/viewjob?jk=1e2347d9cb82b32b</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Forward Deployed Analytics Engineer</t>
+          <t>Devops Engineer II</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Datavations</t>
+          <t>Verisk</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Terraform, Snowflake, BigQuery, Tableau, Power BI, SQL, R</t>
+          <t>S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b666bb6b23815e5</t>
+          <t>https://www.indeed.com/viewjob?jk=ce68c41a7d1fadf5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior AI / Software Engineer (Hybrid / Onsite) — W2 or 1099</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>APLOMB Technologies</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1147,11 +1147,11 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, S3, Glue, Redshift, Data Lake, Redshift, Hadoop, Python, SQL, R</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,102 +1161,102 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4bcb0384662c5e</t>
+          <t>https://www.indeed.com/viewjob?jk=e9a0d061adef57ed</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Scientist - US Card (Applied GenAI)</t>
+          <t>Full Stack Generative AI Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>JSR Tech Consulting</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, LLaMA, Hugging Face, PyTorch, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, FastAPI, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d91ed5378a7a0c79</t>
+          <t>https://www.indeed.com/viewjob?jk=445a580366032112</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Research Associate</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Illinois Institute of Technology</t>
+          <t>The Emmes Company, LLC</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Keras, Git, Matplotlib, Seaborn, Python, SQL, R</t>
+          <t>AI Engineer, Data Scientist, TensorFlow, PyTorch, AWS SageMaker, S3, Redshift, Git, Redshift, Python</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a24879d6afd13b0</t>
+          <t>https://www.indeed.com/viewjob?jk=92f7ff12e06af5cf</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AI Business Analyst (Forward Deployment Engineer)</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>VBEST Software Inc</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, Prompt Engineering, Git, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, LangChain, RAG, TensorFlow, PyTorch, CI/CD, Python, R</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a38f2fe857284a24</t>
+          <t>https://www.indeed.com/viewjob?jk=fc14b923db3f250b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>AWS Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mainspring Energy</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Menlo Park, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R</t>
+          <t>S3, Docker, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Quicksight, Python, SQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61508561e3230b79</t>
+          <t>https://www.indeed.com/viewjob?jk=477b756caf879e2b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Azure AI Engineer</t>
+          <t>Architect â€“ AI / Agentic Automation</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>itecksoft INC.</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Azure ML, GitHub Actions, Git, Python, R, Scala</t>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,242 +1336,242 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3126be45dbf595f6</t>
+          <t>https://www.indeed.com/viewjob?jk=49e0891c14c2cdaa</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>GTM AI Operations Specialist</t>
+          <t>Sr. Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
+          <t>Confiz</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Gemini, Copilot, Prompt Engineering, Git, Snowflake, Databricks, Power BI, SQL, R</t>
+          <t>Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d70712380586eae0</t>
+          <t>https://www.indeed.com/viewjob?jk=56c5376931b082e1</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Simulation Platform</t>
+          <t>Senior Software Development Engineer, IT MFG &amp; TPG</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, NoSQL, Python, SQL, R, Java</t>
+          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, Git, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b14495b26afd48c4</t>
+          <t>https://www.indeed.com/viewjob?jk=9cbfe8edc10c3c6c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>GTM Engineer</t>
+          <t>Optimization Engineer – Commercial</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Allegiant Air</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>BigQuery, Git, Snowflake, BigQuery, Python, SQL, R, Java, Scala</t>
+          <t>Generative AI, Copilot, TensorFlow, PyTorch, Git, Python, SQL, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9e1ccd4183b923a</t>
+          <t>https://www.indeed.com/viewjob?jk=a2657125a5b46def</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (SRE)</t>
+          <t>Senior Engineer- System Integration</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Badger Meter</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+          <t>RAG, S3, EC2, Glue, Git, NoSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6875238a4eff9e2d</t>
+          <t>https://www.indeed.com/viewjob?jk=dbe6975376614e9a</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer III - Python, Pyspark, GKP, Postgress</t>
+          <t>React AWS Javascript ES6 Node.js CDK frameworks (not docker software engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>The Consortium Inc.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Databricks, PySpark, Kafka, Python, R, Java, Scala</t>
+          <t>Copilot, S3, Docker, CI/CD, GitHub Actions, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee4f5783d808292f</t>
+          <t>https://www.indeed.com/viewjob?jk=a3075e05029f2c1b</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Hunter Industries</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>San Marcos, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Docker, Jenkins, Git, Python, SQL, R</t>
+          <t>Data Scientist, RAG, Copilot, Cortex, Snowflake, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb99c3f8ead0f44</t>
+          <t>https://www.indeed.com/viewjob?jk=57257275c845106a</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Junior Data Migration Engineer</t>
+          <t>Sr Software Engineer I</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>RWE</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Git, Python, SQL, R, Java, Optimization</t>
+          <t>RAG, Kubernetes, AKS, Apache Airflow, CI/CD, Terraform, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,42 +1581,1722 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=038cc4f88d870d0a</t>
+          <t>https://www.indeed.com/viewjob?jk=cf874fcd29625031</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Bilt Rewards</t>
+          <t>Domino's</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
+          <t>Ann Arbor, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=45518455fcff213d</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>12127 Sr Mgr AI Engineering &amp; Platform Delivery</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>PSEG</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Newark, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Kubernetes, CI/CD, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=25dec08ab8b5ecba</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Sr. Associate, Software Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>McKesson</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=82e24bf500bf974d</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Cloud Ops Engineer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Modernizing Medicine, Inc.</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Boca Raton, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1cd4f863a0f87618</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>AI Senior Automation Engineer WITH ML/ Deep Learning - 13+ yeras minimum</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>ParsoftLLC</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
           <t>New York, NY, US USA</t>
         </is>
       </c>
-      <c r="D34" t="n">
+      <c r="D38" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Glue, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b39bad4505bb7917</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer SQL</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Valtech Group</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RAG, S3, FastAPI, Terraform, Git, Databricks, Kafka, PostgreSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=01ecd788ad558b31</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Agentic Engineer, Entertainment</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Viasat</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Carlsbad, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, Copilot, Prompt Engineering, BigQuery, CI/CD, Terraform, BigQuery, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=66b3eea3c9dfce6a</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Senior Security Engineer - Data Security</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Sigma Computing</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fcd60009340a0436</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Full Stack AI Engineer</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Micron Technology</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Boise, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Prompt Engineering, Kubernetes, CI/CD, NoSQL, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=822daa46e8a87112</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Micron Technology</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Boise, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, Git, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=68b42d1866024247</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2027 Data &amp; AI Program - Full Time - Analyst - United States</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Copilot, Prompt Engineering, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=723abf4b136be157</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Moody's</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, PyTorch, Docker, Git, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6e3fd80c237c06cf</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Moody's</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Golden, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, PyTorch, Docker, Git, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=78beec1955c1ef25</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Data Analytics Architect</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>SysLogic, Inc.</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Brookfield, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Data Lake, Git, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=88adb284a479dd50</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>MLOps Engineer</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Atomic Machines</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Emeryville, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>AI Engineer, S3, MLflow, Kubernetes, CI/CD, Git, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aa2ac381bee35917</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>TOP RPO LLC</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>RAG, Pinecone, Prompt Engineering, Docker, Kubernetes, Python, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b59c69e1dd6e6029</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Data Scientist 1</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Hoffman Construction Company</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Portland, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Power BI, Matplotlib, Seaborn, Python, SQL, R, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1c6eba44b57c5dc0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Data Scientist I</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Boston Scientific</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Arden Hills, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Keras, Docker, Kubernetes, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b60d558e6d5a5be7</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Applied AI Engineering Intern</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>CCC Intelligent Solutions</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7865284b6bd4fa09</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Intuit</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Mountain View, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Data Scientist, Redshift, BigQuery, Git, BigQuery, Redshift, Tableau, SQL, R, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aa0fae45bfe7bfe2</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Desmata Inc</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0c7c694baa551ea2</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Sybase Data Engineer</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Bridgewater, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Docker, CI/CD, Jenkins, Git, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=feb09db2e1b2d122</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Forward Deployed AI Architect (GenAI, AWS)</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Provectus</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>San Francisco Bay Area, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>AI Engineer, PyTorch, Data Lake, MLflow, Kubernetes, CI/CD, Terraform, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=053a038d949e370b</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Forward Deployed AI Architect (GenAI, AWS)</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Provectus</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>AI Engineer, PyTorch, Data Lake, MLflow, Kubernetes, CI/CD, Terraform, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f747a9ce3c142b8c</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Senior Systems Operations Engineer</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>RAG, Jenkins, Terraform, MongoDB, NoSQL, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e0dc46137d5540db</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Senior Systems Operations Engineer</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>RAG, Jenkins, Terraform, MongoDB, NoSQL, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c29cf9cc795968ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Senior Systems Operations Engineer</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>RAG, Jenkins, Terraform, MongoDB, NoSQL, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bb32cf85e3c1080f</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Senior Systems Operations Engineer</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>RAG, Jenkins, Terraform, MongoDB, NoSQL, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6f2dde3b2260b6b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Senior Systems Operations Engineer</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>RAG, Jenkins, Terraform, MongoDB, NoSQL, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ca87236a3cae5b38</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Engineer-II, Firmware Test Engg</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Micron Technology</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Longmont, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
         <v>10</v>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9607b5ea782aec46</t>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, TensorFlow, PyTorch, CI/CD, Git, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b0be97233abd9c36</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Engineer, FW &amp; Product Test Engineering</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Micron Technology</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Longmont, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Copilot, TensorFlow, PyTorch, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6ccf7feaad154c25</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>AI &amp; Security System Engineer</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Micron Technology</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Boise, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Kubernetes, CI/CD, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3291ef7ea8fc918d</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Engineer - Operations Improvement</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Micron Technology</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Boise, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>RAG, Git, Snowflake, Tableau, Python, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7fac70c9a601e645</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>AI &amp; Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Magnet Forensics</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, Copilot, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=13c6273cd55b22eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Innovation Engineer- Remote (Anywhere in the U.S.)</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>GuidePoint Security</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, S3, Terraform, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1c2717547230f0b2</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>AI Engineer, People Technology</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Micron Technology</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Docker, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0d06851bbcfe236b</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>AI Engineer, People Technology</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Micron Technology</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Boise, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Docker, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1499276deaa11144</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Software Engineer III (AI)</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Ignite Insurance Systems</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Holmdel, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Prompt Engineering, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=759c1c306d11040f</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>AI Developer</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>DIAMONDBACK ENERGY</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1aefc768a4d3ecd3</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2027 Quantitative Analytics Program – Applied Computational Intelligence (ACI Masters) – Early Careers</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b3525446139a887b</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst - Gaming Analytics</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Accel Entertainment Gaming, LLC.</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Burr Ridge, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>RAG, Databricks, Tableau, Power BI, Python, SQL, R, Scala, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a71bad5ef7b2f6db</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=58183cf8c5ef6561</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Research Triangle Park, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=517733c5bdd21a6d</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Milpitas, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Prompt Engineering, Kubernetes, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b26616e269182ac8</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Fullstack AI Engineer</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>G-P</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1cebaf8d6a9402d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Fullstack AI Engineer</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>G-P</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6481b1c1591196e4</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>ELIOR GROUP</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, AKS, CI/CD, Git, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9fc0dd7497b74e1b</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Brook + Whittle</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>RAG, Pinecone, Prompt Engineering, Docker, CI/CD, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=32a77e64ec54435e</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>AI Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Hillwood Development Company, LLC.</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Prompt Engineering, CI/CD, Databricks, Power BI, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5feb80a570658fc1</t>
         </is>
       </c>
     </row>
